--- a/artfynd/A 21220-2025 artfynd.xlsx
+++ b/artfynd/A 21220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124837612</v>
+        <v>124837679</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>96982</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629634</v>
+        <v>629537</v>
       </c>
       <c r="R2" t="n">
-        <v>6543462</v>
+        <v>6543593</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124837679</v>
+        <v>124837612</v>
       </c>
       <c r="B3" t="n">
-        <v>96982</v>
+        <v>79428</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629537</v>
+        <v>629634</v>
       </c>
       <c r="R3" t="n">
-        <v>6543593</v>
+        <v>6543462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 21220-2025 artfynd.xlsx
+++ b/artfynd/A 21220-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124837679</v>
+        <v>124837612</v>
       </c>
       <c r="B2" t="n">
-        <v>96982</v>
+        <v>79428</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629537</v>
+        <v>629634</v>
       </c>
       <c r="R2" t="n">
-        <v>6543593</v>
+        <v>6543462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124837612</v>
+        <v>124837679</v>
       </c>
       <c r="B3" t="n">
-        <v>79428</v>
+        <v>96982</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629634</v>
+        <v>629537</v>
       </c>
       <c r="R3" t="n">
-        <v>6543462</v>
+        <v>6543593</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 21220-2025 artfynd.xlsx
+++ b/artfynd/A 21220-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124837612</v>
       </c>
       <c r="B2" t="n">
-        <v>79428</v>
+        <v>79565</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>124837679</v>
       </c>
       <c r="B3" t="n">
-        <v>96982</v>
+        <v>97150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 21220-2025 artfynd.xlsx
+++ b/artfynd/A 21220-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124837612</v>
+        <v>124837679</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629634</v>
+        <v>629537</v>
       </c>
       <c r="R2" t="n">
-        <v>6543462</v>
+        <v>6543593</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124837679</v>
+        <v>124837612</v>
       </c>
       <c r="B3" t="n">
-        <v>97150</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>629537</v>
+        <v>629634</v>
       </c>
       <c r="R3" t="n">
-        <v>6543593</v>
+        <v>6543462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 21220-2025 artfynd.xlsx
+++ b/artfynd/A 21220-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124837679</v>
+        <v>124837827</v>
       </c>
       <c r="B2" t="n">
-        <v>97150</v>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grindkärret, Grindkärret, Srm</t>
+          <t>Hopen, Hopen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>629537</v>
+        <v>629141</v>
       </c>
       <c r="R2" t="n">
-        <v>6543593</v>
+        <v>6543616</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>124837612</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -866,6 +866,103 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124837679</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grindkärret, Grindkärret, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>629537</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6543593</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21220-2025 artfynd.xlsx
+++ b/artfynd/A 21220-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124837827</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124837612</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124837679</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>